--- a/output/outage_workbook.xlsx
+++ b/output/outage_workbook.xlsx
@@ -15,17 +15,18 @@
     <sheet name="PADD Detail" sheetId="6" r:id="rId6"/>
     <sheet name="Units" sheetId="7" r:id="rId7"/>
     <sheet name="Refinery Detail" sheetId="8" r:id="rId8"/>
-    <sheet name="Scenario 2027" sheetId="9" r:id="rId9"/>
-    <sheet name="Sensitivity" sheetId="10" r:id="rId10"/>
-    <sheet name="Mogas Overlay" sheetId="11" r:id="rId11"/>
-    <sheet name="Notes" sheetId="12" r:id="rId12"/>
+    <sheet name="Clusters" sheetId="9" r:id="rId9"/>
+    <sheet name="Scenario 2027" sheetId="10" r:id="rId10"/>
+    <sheet name="Sensitivity" sheetId="11" r:id="rId11"/>
+    <sheet name="Mogas Overlay" sheetId="12" r:id="rId12"/>
+    <sheet name="Notes" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="328">
   <si>
     <t>REFINERY OUTAGE ANALYTICS</t>
   </si>
@@ -123,6 +124,12 @@
     <t>Top refineries, operators and event scatter</t>
   </si>
   <si>
+    <t>Clusters</t>
+  </si>
+  <si>
+    <t>Back-to-back outage runs incl. ExxonMobil FCC turnarounds</t>
+  </si>
+  <si>
     <t>Scenario 2027</t>
   </si>
   <si>
@@ -276,6 +283,18 @@
     <t>Guardrail: only Planned is comparable vs 2027 (no actual unplanned-2027 exists).</t>
   </si>
   <si>
+    <t>Unplanned Offline by PADD - Level (kbd)</t>
+  </si>
+  <si>
+    <t>Unplanned Offline by PADD - YoY %</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>PADD 5 swings hardest (California events); PADD 3 is the largest base.</t>
+  </si>
+  <si>
     <t>Monthly Detail &amp; Seasonality</t>
   </si>
   <si>
@@ -381,7 +400,7 @@
     <t>Unit-Category Detail</t>
   </si>
   <si>
-    <t>Capacity offline (kbd) by unit category x year, sorted by total.</t>
+    <t>Capacity offline (kbd) by unit category x year, with share of total and YoY%.</t>
   </si>
   <si>
     <t>Capacity Offline by Unit Category (kbd)</t>
@@ -390,6 +409,9 @@
     <t>Unit Category</t>
   </si>
   <si>
+    <t>% of '25</t>
+  </si>
+  <si>
     <t>Atmos Distillation</t>
   </si>
   <si>
@@ -546,6 +568,156 @@
     <t>Capacity (kbd)</t>
   </si>
   <si>
+    <t>Back-to-Back Outage Clusters</t>
+  </si>
+  <si>
+    <t>Consecutive-month outages at one plant/unit - the clustered risk that month-level external trackers wash out.</t>
+  </si>
+  <si>
+    <t>ExxonMobil FCC Capacity Offline (kbd) - Plant x Month, 2022-2026</t>
+  </si>
+  <si>
+    <t>Plant (Year)</t>
+  </si>
+  <si>
+    <t>Baton Rouge 2022</t>
+  </si>
+  <si>
+    <t>Baton Rouge 2023</t>
+  </si>
+  <si>
+    <t>Baton Rouge 2024</t>
+  </si>
+  <si>
+    <t>Baton Rouge 2025</t>
+  </si>
+  <si>
+    <t>Baytown 2022</t>
+  </si>
+  <si>
+    <t>Baytown 2023</t>
+  </si>
+  <si>
+    <t>Baytown 2026</t>
+  </si>
+  <si>
+    <t>Beaumont 2022</t>
+  </si>
+  <si>
+    <t>Beaumont 2023</t>
+  </si>
+  <si>
+    <t>Beaumont 2024</t>
+  </si>
+  <si>
+    <t>Beaumont 2025</t>
+  </si>
+  <si>
+    <t>Beaumont 2026</t>
+  </si>
+  <si>
+    <t>Joliet 2022</t>
+  </si>
+  <si>
+    <t>Joliet 2024</t>
+  </si>
+  <si>
+    <t>Joliet 2025</t>
+  </si>
+  <si>
+    <t>Joliet 2026</t>
+  </si>
+  <si>
+    <t>Shaded runs of adjacent months = back-to-back FCC outages (e.g. Joliet Feb-Jun).</t>
+  </si>
+  <si>
+    <t>ExxonMobil FCC Back-to-Back Runs (&gt;=3 consecutive months, ex-2020)</t>
+  </si>
+  <si>
+    <t>Span</t>
+  </si>
+  <si>
+    <t>Months</t>
+  </si>
+  <si>
+    <t>kbd</t>
+  </si>
+  <si>
+    <t>Jan-Jun</t>
+  </si>
+  <si>
+    <t>Mar-Aug</t>
+  </si>
+  <si>
+    <t>Feb-Jun</t>
+  </si>
+  <si>
+    <t>Jan-Apr</t>
+  </si>
+  <si>
+    <t>Jul-Oct</t>
+  </si>
+  <si>
+    <t>Aug-Nov</t>
+  </si>
+  <si>
+    <t>Mar-Jun</t>
+  </si>
+  <si>
+    <t>Apr-Jul</t>
+  </si>
+  <si>
+    <t>Feb-May</t>
+  </si>
+  <si>
+    <t>Jan-Mar</t>
+  </si>
+  <si>
+    <t>Feb-Apr</t>
+  </si>
+  <si>
+    <t>May-Jul</t>
+  </si>
+  <si>
+    <t>Apr-Jun</t>
+  </si>
+  <si>
+    <t>Sep-Nov</t>
+  </si>
+  <si>
+    <t>Notable Multi-Month Clusters - All Operators (&gt;=4 months, ex-2020)</t>
+  </si>
+  <si>
+    <t>Mo</t>
+  </si>
+  <si>
+    <t>Jan-Dec</t>
+  </si>
+  <si>
+    <t>Torrance Refinery</t>
+  </si>
+  <si>
+    <t>Torrance Refining Company Llc</t>
+  </si>
+  <si>
+    <t>Pasadena Refinery</t>
+  </si>
+  <si>
+    <t>Borger Refinery</t>
+  </si>
+  <si>
+    <t>Superior Refinery</t>
+  </si>
+  <si>
+    <t>Corpus Christi Refinery - East (CITGO)</t>
+  </si>
+  <si>
+    <t>Chalmette Refinery</t>
+  </si>
+  <si>
+    <t>Chalmette Refining Llc</t>
+  </si>
+  <si>
     <t>2027 Unplanned Scenario (Live Model)</t>
   </si>
   <si>
@@ -624,13 +796,19 @@
     <t>2024 Unplanned (actual)</t>
   </si>
   <si>
-    <t>2027 Scenario - PADD Allocation (by historical unplanned share)</t>
+    <t>2027 Scenario by PADD - each PADD's own seasonality (live)</t>
+  </si>
+  <si>
+    <t>Baseline (kbd)</t>
+  </si>
+  <si>
+    <t>Scenario (kbd)</t>
   </si>
   <si>
     <t>Share</t>
   </si>
   <si>
-    <t>Scenario kbd</t>
+    <t>Sums to the national unplanned forecast above; growth &amp; multiplier apply per PADD.</t>
   </si>
   <si>
     <t>Sensitivity &amp; Risk</t>
@@ -793,6 +971,12 @@
   </si>
   <si>
     <t>Mogas-eq = capacity x bucket yield (CDU .175, FCC .65, Ref .85, HDC .05, Coker .20, else 0). Additive overlay; capacity never discarded.</t>
+  </si>
+  <si>
+    <t>Cluster method</t>
+  </si>
+  <si>
+    <t>Back-to-back = consecutive calendar months of outage at one plant/unit within a year (2020 excluded). Surfaces clustered FCC turnarounds that month-level external trackers miss.</t>
   </si>
   <si>
     <t>Refresh</t>
@@ -832,14 +1016,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="#,##0"/>
     <numFmt numFmtId="165" formatCode="0%"/>
     <numFmt numFmtId="166" formatCode="@"/>
     <numFmt numFmtId="167" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="0.0&quot;x&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="#,##0;;&quot;&quot;"/>
+    <numFmt numFmtId="170" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -960,6 +1145,12 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
@@ -969,12 +1160,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1045,13 +1230,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFC55A11"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC55A11"/>
+        <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1062,7 +1247,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1082,6 +1267,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE0E0E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE0E0E0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1149,7 +1349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1234,55 +1434,58 @@
     <xf numFmtId="167" fontId="15" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="18" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="16" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6351,6 +6554,23 @@
               </a:solidFill>
             </c:spPr>
           </c:dPt>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="FFFFFF"/>
+                    </a:solidFill>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showPercent val="1"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Dashboard!$B$62:$B$66</c:f>
@@ -11267,7 +11487,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
+      <xdr:colOff>247650</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -11719,7 +11939,7 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A2:H30"/>
+  <dimension ref="A2:H31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -12024,8 +12244,21 @@
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="C7:H7"/>
@@ -12050,6 +12283,7 @@
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C31:H31"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B20" location="'Dashboard'!A1" display="Dashboard"/>
@@ -12059,16 +12293,938 @@
     <hyperlink ref="B24" location="'PADD Detail'!A1" display="PADD Detail"/>
     <hyperlink ref="B25" location="'Units'!A1" display="Units"/>
     <hyperlink ref="B26" location="'Refinery Detail'!A1" display="Refinery Detail"/>
-    <hyperlink ref="B27" location="'Scenario 2027'!A1" display="Scenario 2027"/>
-    <hyperlink ref="B28" location="'Sensitivity'!A1" display="Sensitivity"/>
-    <hyperlink ref="B29" location="'Mogas Overlay'!A1" display="Mogas Overlay"/>
-    <hyperlink ref="B30" location="'Notes'!A1" display="Notes"/>
+    <hyperlink ref="B27" location="'Clusters'!A1" display="Clusters"/>
+    <hyperlink ref="B28" location="'Scenario 2027'!A1" display="Scenario 2027"/>
+    <hyperlink ref="B29" location="'Sensitivity'!A1" display="Sensitivity"/>
+    <hyperlink ref="B30" location="'Mogas Overlay'!A1" display="Mogas Overlay"/>
+    <hyperlink ref="B31" location="'Notes'!A1" display="Notes"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFC00000"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:N63"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="2.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="14" width="9.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:14">
+      <c r="B2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="2:14">
+      <c r="B3" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+    </row>
+    <row r="6" spans="2:14" ht="20" customHeight="1">
+      <c r="B6" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="B8" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8" s="34">
+        <v>0</v>
+      </c>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+    </row>
+    <row r="9" spans="2:14">
+      <c r="B9" s="32" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="35">
+        <v>1</v>
+      </c>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+    </row>
+    <row r="10" spans="2:14">
+      <c r="B10" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" s="36">
+        <v>0</v>
+      </c>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+    </row>
+    <row r="11" spans="2:14">
+      <c r="B11" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+    </row>
+    <row r="13" spans="2:14" ht="20" customHeight="1">
+      <c r="B13" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+    </row>
+    <row r="14" spans="2:14">
+      <c r="B14" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="N14" s="15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
+      <c r="B15" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="C15" s="17">
+        <v>2282.61105</v>
+      </c>
+      <c r="D15" s="17">
+        <v>3072.01685</v>
+      </c>
+      <c r="E15" s="17">
+        <v>2313.48415</v>
+      </c>
+      <c r="F15" s="17">
+        <v>2274.507825</v>
+      </c>
+      <c r="G15" s="17">
+        <v>1589.601875</v>
+      </c>
+      <c r="H15" s="17">
+        <v>1370.05175</v>
+      </c>
+      <c r="I15" s="17">
+        <v>1306.436325</v>
+      </c>
+      <c r="J15" s="17">
+        <v>1245.677625</v>
+      </c>
+      <c r="K15" s="17">
+        <v>1515.4383</v>
+      </c>
+      <c r="L15" s="17">
+        <v>2050.317675</v>
+      </c>
+      <c r="M15" s="17">
+        <v>1344.783825</v>
+      </c>
+      <c r="N15" s="17">
+        <v>1425.26985</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
+      <c r="B16" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="C16" s="17">
+        <v>2331.3456</v>
+      </c>
+      <c r="D16" s="17">
+        <v>3242.643133333333</v>
+      </c>
+      <c r="E16" s="17">
+        <v>2452.0467</v>
+      </c>
+      <c r="F16" s="17">
+        <v>2323.8248</v>
+      </c>
+      <c r="G16" s="17">
+        <v>1480.8669</v>
+      </c>
+      <c r="H16" s="17">
+        <v>1371.5984</v>
+      </c>
+      <c r="I16" s="17">
+        <v>1295.816366666667</v>
+      </c>
+      <c r="J16" s="17">
+        <v>1211.909366666667</v>
+      </c>
+      <c r="K16" s="17">
+        <v>1621.180633333333</v>
+      </c>
+      <c r="L16" s="17">
+        <v>2132.550833333333</v>
+      </c>
+      <c r="M16" s="17">
+        <v>1240.659633333333</v>
+      </c>
+      <c r="N16" s="17">
+        <v>806.3173666666667</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="C17" s="17">
+        <v>1933.502583333333</v>
+      </c>
+      <c r="D17" s="17">
+        <v>2767.98955</v>
+      </c>
+      <c r="E17" s="17">
+        <v>2082.86935</v>
+      </c>
+      <c r="F17" s="17">
+        <v>2054.312466666667</v>
+      </c>
+      <c r="G17" s="17">
+        <v>1459.746016666667</v>
+      </c>
+      <c r="H17" s="17">
+        <v>1224.888666666667</v>
+      </c>
+      <c r="I17" s="17">
+        <v>1258.94175</v>
+      </c>
+      <c r="J17" s="17">
+        <v>1115.338283333333</v>
+      </c>
+      <c r="K17" s="17">
+        <v>1463.838083333333</v>
+      </c>
+      <c r="L17" s="17">
+        <v>1795.539</v>
+      </c>
+      <c r="M17" s="17">
+        <v>1192.92015</v>
+      </c>
+      <c r="N17" s="17">
+        <v>1127.578033333333</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C18" s="17">
+        <v>1643.7977</v>
+      </c>
+      <c r="D18" s="17">
+        <v>2083.21442</v>
+      </c>
+      <c r="E18" s="17">
+        <v>1614.52331</v>
+      </c>
+      <c r="F18" s="17">
+        <v>1584.22778</v>
+      </c>
+      <c r="G18" s="17">
+        <v>1154.09354</v>
+      </c>
+      <c r="H18" s="17">
+        <v>997.7466400000001</v>
+      </c>
+      <c r="I18" s="17">
+        <v>999.65198</v>
+      </c>
+      <c r="J18" s="17">
+        <v>1210.45329</v>
+      </c>
+      <c r="K18" s="17">
+        <v>1988.70389</v>
+      </c>
+      <c r="L18" s="17">
+        <v>1586.17207</v>
+      </c>
+      <c r="M18" s="17">
+        <v>1044.36847</v>
+      </c>
+      <c r="N18" s="17">
+        <v>916.2710999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" ht="20" customHeight="1">
+      <c r="B20" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21" s="14"/>
+      <c r="C21" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="N21" s="15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="C22" s="17">
+        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),1)</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="17">
+        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),2)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="17">
+        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),3)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="17">
+        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),4)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="17">
+        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),5)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="17">
+        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),6)</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="17">
+        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),7)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="17">
+        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),8)</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="17">
+        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),9)</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="17">
+        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),10)</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="17">
+        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),11)</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="17">
+        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="C23" s="37">
+        <f>C22*(1+$C$8)*$C$9+IF($C$11=C21,$C$10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="37">
+        <f>D22*(1+$C$8)*$C$9+IF($C$11=D21,$C$10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="37">
+        <f>E22*(1+$C$8)*$C$9+IF($C$11=E21,$C$10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="37">
+        <f>F22*(1+$C$8)*$C$9+IF($C$11=F21,$C$10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="37">
+        <f>G22*(1+$C$8)*$C$9+IF($C$11=G21,$C$10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="37">
+        <f>H22*(1+$C$8)*$C$9+IF($C$11=H21,$C$10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="37">
+        <f>I22*(1+$C$8)*$C$9+IF($C$11=I21,$C$10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="37">
+        <f>J22*(1+$C$8)*$C$9+IF($C$11=J21,$C$10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="37">
+        <f>K22*(1+$C$8)*$C$9+IF($C$11=K21,$C$10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="37">
+        <f>L22*(1+$C$8)*$C$9+IF($C$11=L21,$C$10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="37">
+        <f>M22*(1+$C$8)*$C$9+IF($C$11=M21,$C$10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="37">
+        <f>N22*(1+$C$8)*$C$9+IF($C$11=N21,$C$10,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" ht="20" customHeight="1">
+      <c r="B25" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="C26" s="17">
+        <f>SUM(C22:N22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="C27" s="37">
+        <f>SUM(C23:N23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="C28" s="38">
+        <v>15923.1696</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="C29" s="37">
+        <f>$C$27+$C$28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" ht="20" customHeight="1">
+      <c r="B31" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J32" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="L32" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="M32" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="N32" s="15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14">
+      <c r="B33" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="C33" s="17">
+        <f>C23</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="17">
+        <f>D23</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="17">
+        <f>E23</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="17">
+        <f>F23</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="17">
+        <f>G23</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="17">
+        <f>H23</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="17">
+        <f>I23</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="17">
+        <f>J23</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="17">
+        <f>K23</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="17">
+        <f>L23</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="17">
+        <f>M23</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="17">
+        <f>N23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14">
+      <c r="B34" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="17">
+        <v>1088.333</v>
+      </c>
+      <c r="D34" s="17">
+        <v>2092.4001</v>
+      </c>
+      <c r="E34" s="17">
+        <v>2910.1523</v>
+      </c>
+      <c r="F34" s="17">
+        <v>2004.0124</v>
+      </c>
+      <c r="G34" s="17">
+        <v>901.152</v>
+      </c>
+      <c r="H34" s="17">
+        <v>215.305</v>
+      </c>
+      <c r="I34" s="17">
+        <v>167.5</v>
+      </c>
+      <c r="J34" s="17">
+        <v>51.06</v>
+      </c>
+      <c r="K34" s="17">
+        <v>2986.8719</v>
+      </c>
+      <c r="L34" s="17">
+        <v>2955.9469</v>
+      </c>
+      <c r="M34" s="17">
+        <v>546.936</v>
+      </c>
+      <c r="N34" s="17">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14">
+      <c r="B35" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C35" s="17">
+        <v>1400.9949</v>
+      </c>
+      <c r="D35" s="17">
+        <v>2023.3805</v>
+      </c>
+      <c r="E35" s="17">
+        <v>2228.4465</v>
+      </c>
+      <c r="F35" s="17">
+        <v>2621.2351</v>
+      </c>
+      <c r="G35" s="17">
+        <v>1753.1826</v>
+      </c>
+      <c r="H35" s="17">
+        <v>1169.5851</v>
+      </c>
+      <c r="I35" s="17">
+        <v>939.4538</v>
+      </c>
+      <c r="J35" s="17">
+        <v>979.7175</v>
+      </c>
+      <c r="K35" s="17">
+        <v>1487.0255</v>
+      </c>
+      <c r="L35" s="17">
+        <v>2468.751</v>
+      </c>
+      <c r="M35" s="17">
+        <v>1324.048</v>
+      </c>
+      <c r="N35" s="17">
+        <v>861.7330000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14">
+      <c r="B36" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="C36" s="17">
+        <v>2433.6238</v>
+      </c>
+      <c r="D36" s="17">
+        <v>5025.1422</v>
+      </c>
+      <c r="E36" s="17">
+        <v>2051.1556</v>
+      </c>
+      <c r="F36" s="17">
+        <v>1881.5364</v>
+      </c>
+      <c r="G36" s="17">
+        <v>940.6905</v>
+      </c>
+      <c r="H36" s="17">
+        <v>1023.714</v>
+      </c>
+      <c r="I36" s="17">
+        <v>1472.8685</v>
+      </c>
+      <c r="J36" s="17">
+        <v>1211.9996</v>
+      </c>
+      <c r="K36" s="17">
+        <v>1844.9944</v>
+      </c>
+      <c r="L36" s="17">
+        <v>1940.158</v>
+      </c>
+      <c r="M36" s="17">
+        <v>1047.007</v>
+      </c>
+      <c r="N36" s="17">
+        <v>709.6768</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" ht="20" customHeight="1">
+      <c r="B55" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="C55" s="27"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+    </row>
+    <row r="56" spans="2:5">
+      <c r="B56" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5">
+      <c r="B57" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" s="17">
+        <v>1000.115125</v>
+      </c>
+      <c r="D57" s="37">
+        <f>C57*(1+$C$8)*$C$9</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="39">
+        <f>IF($D$62=0,0,D57/$D$62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="B58" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C58" s="17">
+        <v>5461.137000000001</v>
+      </c>
+      <c r="D58" s="37">
+        <f>C58*(1+$C$8)*$C$9</f>
+        <v>0</v>
+      </c>
+      <c r="E58" s="39">
+        <f>IF($D$62=0,0,D58/$D$62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5">
+      <c r="B59" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C59" s="17">
+        <v>10251.807025</v>
+      </c>
+      <c r="D59" s="37">
+        <f>C59*(1+$C$8)*$C$9</f>
+        <v>0</v>
+      </c>
+      <c r="E59" s="39">
+        <f>IF($D$62=0,0,D59/$D$62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5">
+      <c r="B60" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60" s="17">
+        <v>736.9075499999999</v>
+      </c>
+      <c r="D60" s="37">
+        <f>C60*(1+$C$8)*$C$9</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="39">
+        <f>IF($D$62=0,0,D60/$D$62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5">
+      <c r="B61" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C61" s="17">
+        <v>4340.230399999999</v>
+      </c>
+      <c r="D61" s="37">
+        <f>C61*(1+$C$8)*$C$9</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="39">
+        <f>IF($D$62=0,0,D61/$D$62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5">
+      <c r="B62" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C62" s="37">
+        <f>SUM(C57:C61)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="37">
+        <f>SUM(D57:D61)</f>
+        <v>0</v>
+      </c>
+      <c r="E62" s="39">
+        <f>IF($D$62=0,0,SUM(E57:E61))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5">
+      <c r="B63" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="B13:N13"/>
+    <mergeCell ref="B20:N20"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B55:E55"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7">
+      <formula1>"2022-2025,2023-2025,2018-19 &amp; 22-25,All ex-2020/21"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11">
+      <formula1>"Jan,Feb,Mar,Apr,May,Jun,Jul,Aug,Sep,Oct,Nov,Dec"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" fitToHeight="0" orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FFC55A11"/>
@@ -12084,7 +13240,7 @@
   <sheetData>
     <row r="2" spans="2:11">
       <c r="B2" s="1" t="s">
-        <v>202</v>
+        <v>261</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -12098,7 +13254,7 @@
     </row>
     <row r="3" spans="2:11">
       <c r="B3" s="2" t="s">
-        <v>203</v>
+        <v>262</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -12111,251 +13267,251 @@
       <c r="K3" s="2"/>
     </row>
     <row r="6" spans="2:11" ht="20" customHeight="1">
-      <c r="B6" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
+      <c r="B6" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
     </row>
     <row r="7" spans="2:11">
-      <c r="B7" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="C7" s="40">
+      <c r="B7" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" s="41">
         <v>0.7</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="41">
         <v>0.85</v>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="41">
         <v>1</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="41">
         <v>1.15</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="41">
         <v>1.3</v>
       </c>
-      <c r="H7" s="40">
+      <c r="H7" s="41">
         <v>1.5</v>
       </c>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="41">
+      <c r="B8" s="42">
         <v>-0.1</v>
       </c>
-      <c r="C8" s="42">
+      <c r="C8" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B8)*C$7</f>
         <v>0</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B8)*D$7</f>
         <v>0</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B8)*E$7</f>
         <v>0</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B8)*F$7</f>
         <v>0</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B8)*G$7</f>
         <v>0</v>
       </c>
-      <c r="H8" s="42">
+      <c r="H8" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B8)*H$7</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="41">
+      <c r="B9" s="42">
         <v>-0.05</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B9)*C$7</f>
         <v>0</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B9)*D$7</f>
         <v>0</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B9)*E$7</f>
         <v>0</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B9)*F$7</f>
         <v>0</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B9)*G$7</f>
         <v>0</v>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B9)*H$7</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="41">
-        <v>0</v>
-      </c>
-      <c r="C10" s="42">
+      <c r="B10" s="42">
+        <v>0</v>
+      </c>
+      <c r="C10" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B10)*C$7</f>
         <v>0</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B10)*D$7</f>
         <v>0</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="44">
         <f>'Scenario 2027'!$C$26*(1+$B10)*E$7</f>
         <v>0</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B10)*F$7</f>
         <v>0</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B10)*G$7</f>
         <v>0</v>
       </c>
-      <c r="H10" s="42">
+      <c r="H10" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B10)*H$7</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="41">
+      <c r="B11" s="42">
         <v>0.05</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B11)*C$7</f>
         <v>0</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B11)*D$7</f>
         <v>0</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B11)*E$7</f>
         <v>0</v>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B11)*F$7</f>
         <v>0</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B11)*G$7</f>
         <v>0</v>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B11)*H$7</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="41">
+      <c r="B12" s="42">
         <v>0.1</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B12)*C$7</f>
         <v>0</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B12)*D$7</f>
         <v>0</v>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B12)*E$7</f>
         <v>0</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B12)*F$7</f>
         <v>0</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B12)*G$7</f>
         <v>0</v>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B12)*H$7</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="41">
+      <c r="B13" s="42">
         <v>0.15</v>
       </c>
-      <c r="C13" s="42">
+      <c r="C13" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B13)*C$7</f>
         <v>0</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B13)*D$7</f>
         <v>0</v>
       </c>
-      <c r="E13" s="42">
+      <c r="E13" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B13)*E$7</f>
         <v>0</v>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B13)*F$7</f>
         <v>0</v>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B13)*G$7</f>
         <v>0</v>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="43">
         <f>'Scenario 2027'!$C$26*(1+$B13)*H$7</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:11">
       <c r="B14" s="2" t="s">
-        <v>206</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="20" customHeight="1">
-      <c r="B17" s="38" t="s">
-        <v>207</v>
-      </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
+      <c r="B17" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
     </row>
     <row r="18" spans="2:7">
       <c r="B18" s="14" t="s">
-        <v>208</v>
+        <v>267</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>209</v>
+        <v>268</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>210</v>
+        <v>269</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>211</v>
+        <v>270</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>212</v>
+        <v>271</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>213</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="2:7">
       <c r="B19" s="18" t="s">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c r="C19" s="17">
         <v>15253.13797</v>
@@ -12377,7 +13533,7 @@
     </row>
     <row r="20" spans="2:7">
       <c r="B20" s="18" t="s">
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="C20" s="17">
         <v>18521.667535</v>
@@ -12399,7 +13555,7 @@
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="18" t="s">
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="C21" s="17">
         <v>19611.17739</v>
@@ -12421,7 +13577,7 @@
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="18" t="s">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="C22" s="17">
         <v>21790.1971</v>
@@ -12466,7 +13622,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF548235"/>
@@ -12485,7 +13641,7 @@
   <sheetData>
     <row r="2" spans="2:6">
       <c r="B2" s="1" t="s">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -12494,7 +13650,7 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="2" t="s">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -12503,7 +13659,7 @@
     </row>
     <row r="6" spans="2:6" ht="20" customHeight="1">
       <c r="B6" s="27" t="s">
-        <v>220</v>
+        <v>279</v>
       </c>
       <c r="C6" s="27"/>
       <c r="D6" s="27"/>
@@ -12511,84 +13667,84 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="14" t="s">
-        <v>221</v>
+        <v>280</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>222</v>
+        <v>281</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>223</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" s="44">
+        <v>283</v>
+      </c>
+      <c r="C8" s="45">
         <v>0.175</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>225</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="2:6">
       <c r="B9" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="C9" s="44">
+        <v>285</v>
+      </c>
+      <c r="C9" s="45">
         <v>0.65</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="2:6">
       <c r="B10" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="C10" s="44">
+        <v>286</v>
+      </c>
+      <c r="C10" s="45">
         <v>0.85</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="C11" s="44">
+        <v>287</v>
+      </c>
+      <c r="C11" s="45">
         <v>0.05</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>229</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="2:6">
       <c r="B12" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="C12" s="44">
+        <v>289</v>
+      </c>
+      <c r="C12" s="45">
         <v>0.2</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>231</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="2:6">
       <c r="B13" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="C13" s="44">
+        <v>137</v>
+      </c>
+      <c r="C13" s="45">
         <v>0</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>232</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="20" customHeight="1">
       <c r="B16" s="27" t="s">
-        <v>233</v>
+        <v>292</v>
       </c>
       <c r="C16" s="27"/>
       <c r="D16" s="27"/>
@@ -12596,16 +13752,16 @@
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="2:5">
@@ -12801,12 +13957,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF7F7F7F"/>
   </sheetPr>
-  <dimension ref="B2:H23"/>
+  <dimension ref="B2:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -12816,7 +13972,7 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>234</v>
+        <v>293</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -12827,10 +13983,10 @@
     </row>
     <row r="5" spans="2:8" ht="30" customHeight="1">
       <c r="B5" s="3" t="s">
-        <v>235</v>
+        <v>294</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>236</v>
+        <v>295</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -12843,7 +13999,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -12853,10 +14009,10 @@
     </row>
     <row r="7" spans="2:8" ht="30" customHeight="1">
       <c r="B7" s="3" t="s">
-        <v>238</v>
+        <v>297</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>239</v>
+        <v>298</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -12869,7 +14025,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>240</v>
+        <v>299</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -12879,10 +14035,10 @@
     </row>
     <row r="9" spans="2:8" ht="30" customHeight="1">
       <c r="B9" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -12892,10 +14048,10 @@
     </row>
     <row r="10" spans="2:8" ht="30" customHeight="1">
       <c r="B10" s="3" t="s">
-        <v>242</v>
+        <v>301</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -12905,10 +14061,10 @@
     </row>
     <row r="11" spans="2:8" ht="30" customHeight="1">
       <c r="B11" s="3" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -12918,10 +14074,10 @@
     </row>
     <row r="12" spans="2:8" ht="30" customHeight="1">
       <c r="B12" s="3" t="s">
-        <v>246</v>
+        <v>305</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>247</v>
+        <v>306</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -12931,10 +14087,10 @@
     </row>
     <row r="13" spans="2:8" ht="30" customHeight="1">
       <c r="B13" s="3" t="s">
-        <v>248</v>
+        <v>307</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>249</v>
+        <v>308</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -12944,10 +14100,10 @@
     </row>
     <row r="14" spans="2:8" ht="30" customHeight="1">
       <c r="B14" s="3" t="s">
-        <v>250</v>
+        <v>309</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>251</v>
+        <v>310</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -12957,10 +14113,10 @@
     </row>
     <row r="15" spans="2:8" ht="30" customHeight="1">
       <c r="B15" s="3" t="s">
-        <v>252</v>
+        <v>311</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -12970,10 +14126,10 @@
     </row>
     <row r="16" spans="2:8" ht="30" customHeight="1">
       <c r="B16" s="3" t="s">
-        <v>254</v>
+        <v>313</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -12983,10 +14139,10 @@
     </row>
     <row r="17" spans="2:8" ht="30" customHeight="1">
       <c r="B17" s="3" t="s">
-        <v>256</v>
+        <v>315</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -12994,36 +14150,36 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
-    <row r="19" spans="2:8" ht="20" customHeight="1">
-      <c r="B19" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+    <row r="18" spans="2:8" ht="30" customHeight="1">
+      <c r="B18" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="20" spans="2:8" ht="20" customHeight="1">
+      <c r="B20" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="46" t="s">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>262</v>
+        <v>321</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -13033,10 +14189,10 @@
     </row>
     <row r="22" spans="2:8">
       <c r="B22" s="47" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>264</v>
+        <v>323</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -13046,10 +14202,10 @@
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="48" t="s">
-        <v>265</v>
+        <v>324</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>266</v>
+        <v>325</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -13057,8 +14213,21 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="49" t="s">
+        <v>326</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="C6:H6"/>
@@ -13073,11 +14242,12 @@
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="C16:H16"/>
     <mergeCell ref="C17:H17"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="B20:H20"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="C22:H22"/>
     <mergeCell ref="C23:H23"/>
+    <mergeCell ref="C24:H24"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13098,7 +14268,7 @@
   <sheetData>
     <row r="2" spans="2:13">
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -13114,7 +14284,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -13130,23 +14300,23 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K5" s="9"/>
     </row>
@@ -13168,7 +14338,7 @@
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K6" s="12"/>
     </row>
@@ -13186,40 +14356,40 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K8" s="13"/>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="2:4">
@@ -13334,12 +14504,12 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C54" s="16">
         <v>2022</v>
@@ -13356,7 +14526,7 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C55" s="17">
         <v>838.49</v>
@@ -13373,7 +14543,7 @@
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C56" s="17">
         <v>6764.0168</v>
@@ -13390,7 +14560,7 @@
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C57" s="17">
         <v>11315.8739</v>
@@ -13407,7 +14577,7 @@
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C58" s="17">
         <v>693.9537</v>
@@ -13424,7 +14594,7 @@
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C59" s="17">
         <v>3016.1748</v>
@@ -13441,12 +14611,12 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C62" s="17">
         <v>1524.7432</v>
@@ -13454,7 +14624,7 @@
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C63" s="17">
         <v>2837.6686</v>
@@ -13462,7 +14632,7 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C64" s="17">
         <v>6051.7432</v>
@@ -13470,7 +14640,7 @@
     </row>
     <row r="65" spans="2:3">
       <c r="B65" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C65" s="17">
         <v>381.1887</v>
@@ -13478,7 +14648,7 @@
     </row>
     <row r="66" spans="2:3">
       <c r="B66" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C66" s="17">
         <v>8462.209800000001</v>
@@ -13516,7 +14686,7 @@
     <tabColor rgb="FF2E5496"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:I39"/>
+  <dimension ref="B2:J57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -13526,7 +14696,7 @@
   <sheetData>
     <row r="2" spans="2:9">
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -13538,7 +14708,7 @@
     </row>
     <row r="3" spans="2:9">
       <c r="B3" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -13550,7 +14720,7 @@
     </row>
     <row r="6" spans="2:9" ht="20" customHeight="1">
       <c r="B6" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -13562,28 +14732,28 @@
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="2:9">
@@ -13942,10 +15112,10 @@
     </row>
     <row r="20" spans="2:9">
       <c r="B20" s="18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -13956,7 +15126,7 @@
     </row>
     <row r="23" spans="2:9" ht="20" customHeight="1">
       <c r="B23" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -13968,24 +15138,24 @@
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C25" s="17">
         <v>38674.0736</v>
@@ -14004,7 +15174,7 @@
     </row>
     <row r="26" spans="2:9">
       <c r="B26" s="18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C26" s="17">
         <v>19416.5201</v>
@@ -14023,7 +15193,7 @@
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C27" s="17">
         <v>19257.5535</v>
@@ -14042,41 +15212,41 @@
     </row>
     <row r="29" spans="2:9">
       <c r="B29" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F29" s="15" t="s">
         <v>78</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="30" spans="2:9">
       <c r="B30" s="18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C30" s="17">
         <v>38674.0736</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F30" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="2:9">
       <c r="B31" s="18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C31" s="17">
         <v>19416.5201</v>
@@ -14095,58 +15265,58 @@
     </row>
     <row r="32" spans="2:9">
       <c r="B32" s="18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C32" s="17">
         <v>19257.5535</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F32" s="24" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
       <c r="B34" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C34" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" s="15" t="s">
+      <c r="E34" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
+      <c r="B35" s="18" t="s">
         <v>79</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="18" t="s">
-        <v>77</v>
       </c>
       <c r="C35" s="17">
         <v>20278.8578</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F35" s="24" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
       <c r="B36" s="18" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C36" s="17">
         <v>12029.062</v>
@@ -14163,35 +15333,451 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:10">
       <c r="B37" s="18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C37" s="17">
         <v>8249.7958</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F37" s="24" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10">
       <c r="B39" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" ht="20" customHeight="1">
+      <c r="B42" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+    </row>
+    <row r="43" spans="2:10">
+      <c r="B43" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" s="16">
+        <v>2019</v>
+      </c>
+      <c r="D43" s="16">
+        <v>2020</v>
+      </c>
+      <c r="E43" s="16">
+        <v>2021</v>
+      </c>
+      <c r="F43" s="16">
+        <v>2022</v>
+      </c>
+      <c r="G43" s="16">
+        <v>2023</v>
+      </c>
+      <c r="H43" s="16">
+        <v>2024</v>
+      </c>
+      <c r="I43" s="16">
+        <v>2025</v>
+      </c>
+      <c r="J43" s="20">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
+      <c r="B44" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" s="17">
+        <v>1134.9774</v>
+      </c>
+      <c r="D44" s="17">
+        <v>6639.4917</v>
+      </c>
+      <c r="E44" s="17">
+        <v>3499.3643</v>
+      </c>
+      <c r="F44" s="17">
+        <v>838.49</v>
+      </c>
+      <c r="G44" s="17">
+        <v>879.2184999999999</v>
+      </c>
+      <c r="H44" s="17">
+        <v>758.0088</v>
+      </c>
+      <c r="I44" s="17">
+        <v>1524.7432</v>
+      </c>
+      <c r="J44" s="21">
+        <v>341.7187</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
+      <c r="B45" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" s="17">
+        <v>4280.2866</v>
+      </c>
+      <c r="D45" s="17">
+        <v>27603.1455</v>
+      </c>
+      <c r="E45" s="17">
+        <v>11298.4568</v>
+      </c>
+      <c r="F45" s="17">
+        <v>6764.0168</v>
+      </c>
+      <c r="G45" s="17">
+        <v>6640.3387</v>
+      </c>
+      <c r="H45" s="17">
+        <v>5602.5239</v>
+      </c>
+      <c r="I45" s="17">
+        <v>2837.6686</v>
+      </c>
+      <c r="J45" s="21">
+        <v>1689.4067</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10">
+      <c r="B46" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" s="17">
+        <v>9871.7996</v>
+      </c>
+      <c r="D46" s="17">
+        <v>66183.2975</v>
+      </c>
+      <c r="E46" s="17">
+        <v>40953.2259</v>
+      </c>
+      <c r="F46" s="17">
+        <v>11315.8739</v>
+      </c>
+      <c r="G46" s="17">
+        <v>11829.2618</v>
+      </c>
+      <c r="H46" s="17">
+        <v>11810.3492</v>
+      </c>
+      <c r="I46" s="17">
+        <v>6051.7432</v>
+      </c>
+      <c r="J46" s="21">
+        <v>4200.116</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10">
+      <c r="B47" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C47" s="17">
+        <v>40.13650000000001</v>
+      </c>
+      <c r="D47" s="17">
+        <v>2735.7326</v>
+      </c>
+      <c r="E47" s="17">
+        <v>1627.5056</v>
+      </c>
+      <c r="F47" s="17">
+        <v>693.9537</v>
+      </c>
+      <c r="G47" s="17">
+        <v>1470.7124</v>
+      </c>
+      <c r="H47" s="17">
+        <v>401.7754</v>
+      </c>
+      <c r="I47" s="17">
+        <v>381.1887</v>
+      </c>
+      <c r="J47" s="21">
+        <v>173.0774</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10">
+      <c r="B48" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="17">
+        <v>3008.2042</v>
+      </c>
+      <c r="D48" s="17">
+        <v>21618.5782</v>
+      </c>
+      <c r="E48" s="17">
+        <v>9056.141100000001</v>
+      </c>
+      <c r="F48" s="17">
+        <v>3016.1748</v>
+      </c>
+      <c r="G48" s="17">
+        <v>2872.6275</v>
+      </c>
+      <c r="H48" s="17">
+        <v>3009.9095</v>
+      </c>
+      <c r="I48" s="17">
+        <v>8462.209800000001</v>
+      </c>
+      <c r="J48" s="21">
+        <v>1845.477</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="20" customHeight="1">
+      <c r="B50" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="7"/>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="B51" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="16">
+        <v>2019</v>
+      </c>
+      <c r="D51" s="16">
+        <v>2020</v>
+      </c>
+      <c r="E51" s="16">
+        <v>2021</v>
+      </c>
+      <c r="F51" s="16">
+        <v>2022</v>
+      </c>
+      <c r="G51" s="16">
+        <v>2023</v>
+      </c>
+      <c r="H51" s="16">
+        <v>2024</v>
+      </c>
+      <c r="I51" s="16">
+        <v>2025</v>
+      </c>
+      <c r="J51" s="20">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10">
+      <c r="B52" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" s="19">
+        <f>IF(C44=0,"n/a",(D44-C44)/C44)</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="19">
+        <f>IF(D44=0,"n/a",(E44-D44)/D44)</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="19">
+        <f>IF(E44=0,"n/a",(F44-E44)/E44)</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="19">
+        <f>IF(F44=0,"n/a",(G44-F44)/F44)</f>
+        <v>0</v>
+      </c>
+      <c r="H52" s="19">
+        <f>IF(G44=0,"n/a",(H44-G44)/G44)</f>
+        <v>0</v>
+      </c>
+      <c r="I52" s="19">
+        <f>IF(H44=0,"n/a",(I44-H44)/H44)</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="22">
+        <f>IF(I44=0,"n/a",(J44-I44)/I44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10">
+      <c r="B53" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D53" s="19">
+        <f>IF(C45=0,"n/a",(D45-C45)/C45)</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="19">
+        <f>IF(D45=0,"n/a",(E45-D45)/D45)</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="19">
+        <f>IF(E45=0,"n/a",(F45-E45)/E45)</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="19">
+        <f>IF(F45=0,"n/a",(G45-F45)/F45)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="19">
+        <f>IF(G45=0,"n/a",(H45-G45)/G45)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="19">
+        <f>IF(H45=0,"n/a",(I45-H45)/H45)</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="22">
+        <f>IF(I45=0,"n/a",(J45-I45)/I45)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10">
+      <c r="B54" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D54" s="19">
+        <f>IF(C46=0,"n/a",(D46-C46)/C46)</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="19">
+        <f>IF(D46=0,"n/a",(E46-D46)/D46)</f>
+        <v>0</v>
+      </c>
+      <c r="F54" s="19">
+        <f>IF(E46=0,"n/a",(F46-E46)/E46)</f>
+        <v>0</v>
+      </c>
+      <c r="G54" s="19">
+        <f>IF(F46=0,"n/a",(G46-F46)/F46)</f>
+        <v>0</v>
+      </c>
+      <c r="H54" s="19">
+        <f>IF(G46=0,"n/a",(H46-G46)/G46)</f>
+        <v>0</v>
+      </c>
+      <c r="I54" s="19">
+        <f>IF(H46=0,"n/a",(I46-H46)/H46)</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="22">
+        <f>IF(I46=0,"n/a",(J46-I46)/I46)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="B55" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" s="19">
+        <f>IF(C47=0,"n/a",(D47-C47)/C47)</f>
+        <v>0</v>
+      </c>
+      <c r="E55" s="19">
+        <f>IF(D47=0,"n/a",(E47-D47)/D47)</f>
+        <v>0</v>
+      </c>
+      <c r="F55" s="19">
+        <f>IF(E47=0,"n/a",(F47-E47)/E47)</f>
+        <v>0</v>
+      </c>
+      <c r="G55" s="19">
+        <f>IF(F47=0,"n/a",(G47-F47)/F47)</f>
+        <v>0</v>
+      </c>
+      <c r="H55" s="19">
+        <f>IF(G47=0,"n/a",(H47-G47)/G47)</f>
+        <v>0</v>
+      </c>
+      <c r="I55" s="19">
+        <f>IF(H47=0,"n/a",(I47-H47)/H47)</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="22">
+        <f>IF(I47=0,"n/a",(J47-I47)/I47)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10">
+      <c r="B56" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D56" s="19">
+        <f>IF(C48=0,"n/a",(D48-C48)/C48)</f>
+        <v>0</v>
+      </c>
+      <c r="E56" s="19">
+        <f>IF(D48=0,"n/a",(E48-D48)/D48)</f>
+        <v>0</v>
+      </c>
+      <c r="F56" s="19">
+        <f>IF(E48=0,"n/a",(F48-E48)/E48)</f>
+        <v>0</v>
+      </c>
+      <c r="G56" s="19">
+        <f>IF(F48=0,"n/a",(G48-F48)/F48)</f>
+        <v>0</v>
+      </c>
+      <c r="H56" s="19">
+        <f>IF(G48=0,"n/a",(H48-G48)/G48)</f>
+        <v>0</v>
+      </c>
+      <c r="I56" s="19">
+        <f>IF(H48=0,"n/a",(I48-H48)/H48)</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="22">
+        <f>IF(I48=0,"n/a",(J48-I48)/I48)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10">
+      <c r="B57" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="C20:I20"/>
     <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="B50:J50"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" fitToHeight="0" orientation="landscape"/>
@@ -14215,7 +15801,7 @@
   <sheetData>
     <row r="2" spans="2:15">
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -14233,7 +15819,7 @@
     </row>
     <row r="3" spans="2:15">
       <c r="B3" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -14251,7 +15837,7 @@
     </row>
     <row r="6" spans="2:15" ht="20" customHeight="1">
       <c r="B6" s="7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -14269,46 +15855,46 @@
     </row>
     <row r="7" spans="2:15">
       <c r="B7" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:15">
@@ -14763,7 +16349,7 @@
     </row>
     <row r="19" spans="2:15" ht="20" customHeight="1">
       <c r="B19" s="26" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C19" s="26"/>
       <c r="D19" s="26"/>
@@ -14781,46 +16367,46 @@
     </row>
     <row r="20" spans="2:15">
       <c r="B20" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="M20" s="15" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="N20" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="O20" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="2:15">
@@ -15275,7 +16861,7 @@
     </row>
     <row r="32" spans="2:15" ht="20" customHeight="1">
       <c r="B32" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -15293,46 +16879,46 @@
     </row>
     <row r="33" spans="2:15">
       <c r="B33" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I33" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J33" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L33" s="15" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="M33" s="15" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="N33" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="O33" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="2:15">
@@ -15770,7 +17356,7 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -15787,7 +17373,7 @@
     </row>
     <row r="3" spans="2:14">
       <c r="B3" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -15804,7 +17390,7 @@
     </row>
     <row r="6" spans="2:14" ht="20" customHeight="1">
       <c r="B6" s="27" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C6" s="27"/>
       <c r="D6" s="27"/>
@@ -15821,48 +17407,48 @@
     </row>
     <row r="7" spans="2:14">
       <c r="B7" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="N7" s="15" t="s">
         <v>103</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="L7" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="M7" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="N7" s="15" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="8" spans="2:14">
       <c r="B8" s="18" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C8" s="17">
         <v>3.22</v>
@@ -15903,7 +17489,7 @@
     </row>
     <row r="9" spans="2:14">
       <c r="B9" s="18" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C9" s="17">
         <v>29.58</v>
@@ -15944,7 +17530,7 @@
     </row>
     <row r="10" spans="2:14">
       <c r="B10" s="18" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C10" s="17">
         <v>240.51</v>
@@ -15985,7 +17571,7 @@
     </row>
     <row r="11" spans="2:14">
       <c r="B11" s="18" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C11" s="17">
         <v>99.0698</v>
@@ -16026,7 +17612,7 @@
     </row>
     <row r="12" spans="2:14">
       <c r="B12" s="18" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C12" s="17">
         <v>126.05</v>
@@ -16067,7 +17653,7 @@
     </row>
     <row r="13" spans="2:14">
       <c r="B13" s="18" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C13" s="17">
         <v>0</v>
@@ -16108,7 +17694,7 @@
     </row>
     <row r="28" spans="2:14" ht="20" customHeight="1">
       <c r="B28" s="27" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C28" s="27"/>
       <c r="D28" s="27"/>
@@ -16125,48 +17711,48 @@
     </row>
     <row r="29" spans="2:14">
       <c r="B29" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="N29" s="15" t="s">
         <v>103</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="I29" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="L29" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="M29" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="N29" s="15" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="30" spans="2:14">
       <c r="B30" s="18" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C30" s="17">
         <v>0</v>
@@ -16207,7 +17793,7 @@
     </row>
     <row r="31" spans="2:14">
       <c r="B31" s="18" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C31" s="17">
         <v>161.3505</v>
@@ -16248,7 +17834,7 @@
     </row>
     <row r="32" spans="2:14">
       <c r="B32" s="18" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C32" s="17">
         <v>194.6489</v>
@@ -16289,7 +17875,7 @@
     </row>
     <row r="33" spans="2:14">
       <c r="B33" s="18" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C33" s="17">
         <v>82.622</v>
@@ -16330,7 +17916,7 @@
     </row>
     <row r="34" spans="2:14">
       <c r="B34" s="18" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C34" s="17">
         <v>1256.5976</v>
@@ -16371,7 +17957,7 @@
     </row>
     <row r="35" spans="2:14">
       <c r="B35" s="18" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C35" s="17">
         <v>0</v>
@@ -16412,7 +17998,7 @@
     </row>
     <row r="50" spans="2:14" ht="20" customHeight="1">
       <c r="B50" s="27" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C50" s="27"/>
       <c r="D50" s="27"/>
@@ -16429,48 +18015,48 @@
     </row>
     <row r="51" spans="2:14">
       <c r="B51" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G51" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H51" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I51" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J51" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="L51" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="M51" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="N51" s="15" t="s">
         <v>103</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E51" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="G51" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="H51" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="I51" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="J51" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="K51" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="L51" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="M51" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="N51" s="15" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="52" spans="2:14">
       <c r="B52" s="18" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C52" s="17">
         <v>879.5774</v>
@@ -16511,7 +18097,7 @@
     </row>
     <row r="53" spans="2:14">
       <c r="B53" s="18" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C53" s="17">
         <v>275.676</v>
@@ -16552,7 +18138,7 @@
     </row>
     <row r="54" spans="2:14">
       <c r="B54" s="18" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C54" s="17">
         <v>2513.4756</v>
@@ -16593,7 +18179,7 @@
     </row>
     <row r="55" spans="2:14">
       <c r="B55" s="18" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C55" s="17">
         <v>3897.7506</v>
@@ -16634,7 +18220,7 @@
     </row>
     <row r="56" spans="2:14">
       <c r="B56" s="18" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C56" s="17">
         <v>3219.0812</v>
@@ -16675,7 +18261,7 @@
     </row>
     <row r="57" spans="2:14">
       <c r="B57" s="18" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C57" s="17">
         <v>692.313</v>
@@ -16716,7 +18302,7 @@
     </row>
     <row r="72" spans="2:14" ht="20" customHeight="1">
       <c r="B72" s="27" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C72" s="27"/>
       <c r="D72" s="27"/>
@@ -16733,48 +18319,48 @@
     </row>
     <row r="73" spans="2:14">
       <c r="B73" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G73" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H73" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I73" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J73" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K73" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="L73" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="M73" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="N73" s="15" t="s">
         <v>103</v>
-      </c>
-      <c r="C73" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E73" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F73" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="G73" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="H73" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="I73" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="J73" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="K73" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="L73" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="M73" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="N73" s="15" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="74" spans="2:14">
       <c r="B74" s="18" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C74" s="17">
         <v>0</v>
@@ -16815,7 +18401,7 @@
     </row>
     <row r="75" spans="2:14">
       <c r="B75" s="18" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C75" s="17">
         <v>0</v>
@@ -16856,7 +18442,7 @@
     </row>
     <row r="76" spans="2:14">
       <c r="B76" s="18" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C76" s="17">
         <v>63.17959999999999</v>
@@ -16897,7 +18483,7 @@
     </row>
     <row r="77" spans="2:14">
       <c r="B77" s="18" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C77" s="17">
         <v>71.7204</v>
@@ -16938,7 +18524,7 @@
     </row>
     <row r="78" spans="2:14">
       <c r="B78" s="18" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C78" s="17">
         <v>493.348</v>
@@ -16979,7 +18565,7 @@
     </row>
     <row r="79" spans="2:14">
       <c r="B79" s="18" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C79" s="17">
         <v>0</v>
@@ -17020,7 +18606,7 @@
     </row>
     <row r="94" spans="2:14" ht="20" customHeight="1">
       <c r="B94" s="27" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C94" s="27"/>
       <c r="D94" s="27"/>
@@ -17037,48 +18623,48 @@
     </row>
     <row r="95" spans="2:14">
       <c r="B95" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D95" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E95" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F95" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G95" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H95" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I95" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J95" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K95" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="L95" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="M95" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="N95" s="15" t="s">
         <v>103</v>
-      </c>
-      <c r="C95" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D95" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E95" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F95" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="G95" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="H95" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="I95" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="J95" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="K95" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="L95" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="M95" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="N95" s="15" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="96" spans="2:14">
       <c r="B96" s="18" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C96" s="17">
         <v>179.8849</v>
@@ -17119,7 +18705,7 @@
     </row>
     <row r="97" spans="2:14">
       <c r="B97" s="18" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C97" s="17">
         <v>320.38</v>
@@ -17160,7 +18746,7 @@
     </row>
     <row r="98" spans="2:14">
       <c r="B98" s="18" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C98" s="17">
         <v>509.283</v>
@@ -17201,7 +18787,7 @@
     </row>
     <row r="99" spans="2:14">
       <c r="B99" s="18" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C99" s="17">
         <v>533.6799999999999</v>
@@ -17242,7 +18828,7 @@
     </row>
     <row r="100" spans="2:14">
       <c r="B100" s="18" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C100" s="17">
         <v>617.2497999999999</v>
@@ -17283,7 +18869,7 @@
     </row>
     <row r="101" spans="2:14">
       <c r="B101" s="18" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C101" s="17">
         <v>396.02</v>
@@ -17354,7 +18940,7 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -17371,7 +18957,7 @@
     </row>
     <row r="3" spans="2:14">
       <c r="B3" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -17388,7 +18974,7 @@
     </row>
     <row r="6" spans="2:14" ht="20" customHeight="1">
       <c r="B6" s="7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -17403,7 +18989,7 @@
     </row>
     <row r="7" spans="2:14">
       <c r="B7" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" s="16">
         <v>2018</v>
@@ -17438,7 +19024,7 @@
     </row>
     <row r="8" spans="2:14">
       <c r="B8" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8" s="17">
         <v>2893.3769</v>
@@ -17473,7 +19059,7 @@
     </row>
     <row r="9" spans="2:14">
       <c r="B9" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9" s="17">
         <v>8081.7244</v>
@@ -17508,7 +19094,7 @@
     </row>
     <row r="10" spans="2:14">
       <c r="B10" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10" s="17">
         <v>14797.2328</v>
@@ -17543,7 +19129,7 @@
     </row>
     <row r="11" spans="2:14">
       <c r="B11" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C11" s="17">
         <v>1578.74</v>
@@ -17578,7 +19164,7 @@
     </row>
     <row r="12" spans="2:14">
       <c r="B12" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C12" s="17">
         <v>4684.4105</v>
@@ -17613,7 +19199,7 @@
     </row>
     <row r="13" spans="2:14">
       <c r="B13" s="23" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C13" s="25">
         <f>SUM(C8:C12)</f>
@@ -17658,7 +19244,7 @@
     </row>
     <row r="15" spans="2:14" ht="20" customHeight="1">
       <c r="B15" s="5" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -17672,7 +19258,7 @@
     </row>
     <row r="16" spans="2:14">
       <c r="B16" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C16" s="16">
         <v>2018</v>
@@ -17704,7 +19290,7 @@
     </row>
     <row r="17" spans="2:12">
       <c r="B17" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C17" s="17">
         <v>686.5771999999999</v>
@@ -17736,7 +19322,7 @@
     </row>
     <row r="18" spans="2:12">
       <c r="B18" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C18" s="17">
         <v>2968.9009</v>
@@ -17768,7 +19354,7 @@
     </row>
     <row r="19" spans="2:12">
       <c r="B19" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C19" s="17">
         <v>6130.7373</v>
@@ -17800,7 +19386,7 @@
     </row>
     <row r="20" spans="2:12">
       <c r="B20" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C20" s="17">
         <v>397.564</v>
@@ -17832,7 +19418,7 @@
     </row>
     <row r="21" spans="2:12">
       <c r="B21" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C21" s="17">
         <v>1184.8115</v>
@@ -17864,7 +19450,7 @@
     </row>
     <row r="22" spans="2:12">
       <c r="B22" s="23" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C22" s="25">
         <f>SUM(C17:C21)</f>
@@ -17905,7 +19491,7 @@
     </row>
     <row r="24" spans="2:12" ht="20" customHeight="1">
       <c r="B24" s="26" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="26"/>
@@ -17920,7 +19506,7 @@
     </row>
     <row r="25" spans="2:12">
       <c r="B25" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C25" s="16">
         <v>2018</v>
@@ -17955,7 +19541,7 @@
     </row>
     <row r="26" spans="2:12">
       <c r="B26" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C26" s="17">
         <v>2206.7997</v>
@@ -17990,7 +19576,7 @@
     </row>
     <row r="27" spans="2:12">
       <c r="B27" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C27" s="17">
         <v>5112.8235</v>
@@ -18025,7 +19611,7 @@
     </row>
     <row r="28" spans="2:12">
       <c r="B28" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C28" s="17">
         <v>8666.495500000001</v>
@@ -18060,7 +19646,7 @@
     </row>
     <row r="29" spans="2:12">
       <c r="B29" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C29" s="17">
         <v>1181.176</v>
@@ -18095,7 +19681,7 @@
     </row>
     <row r="30" spans="2:12">
       <c r="B30" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C30" s="17">
         <v>3499.599</v>
@@ -18130,7 +19716,7 @@
     </row>
     <row r="31" spans="2:12">
       <c r="B31" s="23" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C31" s="25">
         <f>SUM(C26:C30)</f>
@@ -18193,18 +19779,18 @@
     <tabColor rgb="FFBF9000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L24"/>
+  <dimension ref="B2:N24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" customWidth="1"/>
     <col min="3" max="11" width="9.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="12" max="14" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -18216,10 +19802,12 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -18231,10 +19819,12 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
-    </row>
-    <row r="6" spans="2:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+    </row>
+    <row r="6" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -18245,10 +19835,12 @@
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C7" s="16">
         <v>2020</v>
@@ -18275,12 +19867,18 @@
         <v>2027</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="18" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C8" s="17">
         <v>46512.4768</v>
@@ -18310,10 +19908,18 @@
         <f>SUM(C8:J8)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L8" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H8/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="19">
+        <f>IF(G8=0,"n/a",(H8-G8)/G8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="18" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C9" s="28">
         <v>37292.0667</v>
@@ -18343,10 +19949,18 @@
         <f>SUM(C9:J9)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L9" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H9/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="19">
+        <f>IF(G9=0,"n/a",(H9-G9)/G9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="18" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C10" s="17">
         <v>19361.9278</v>
@@ -18376,10 +19990,18 @@
         <f>SUM(C10:J10)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L10" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H10/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="19">
+        <f>IF(G10=0,"n/a",(H10-G10)/G10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="18" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C11" s="28">
         <v>16430.7895</v>
@@ -18409,10 +20031,18 @@
         <f>SUM(C11:J11)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L11" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H11/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="19">
+        <f>IF(G11=0,"n/a",(H11-G11)/G11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="18" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C12" s="17">
         <v>10878.1816</v>
@@ -18442,10 +20072,18 @@
         <f>SUM(C12:J12)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L12" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H12/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="19">
+        <f>IF(G12=0,"n/a",(H12-G12)/G12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="18" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C13" s="28">
         <v>7296.2186</v>
@@ -18475,10 +20113,18 @@
         <f>SUM(C13:J13)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L13" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H13/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="19">
+        <f>IF(G13=0,"n/a",(H13-G13)/G13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="18" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C14" s="17">
         <v>6316.6157</v>
@@ -18508,10 +20154,18 @@
         <f>SUM(C14:J14)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L14" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H14/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="19">
+        <f>IF(G14=0,"n/a",(H14-G14)/G14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="18" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C15" s="28">
         <v>3199.133</v>
@@ -18541,10 +20195,18 @@
         <f>SUM(C15:J15)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L15" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H15/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="19">
+        <f>IF(G15=0,"n/a",(H15-G15)/G15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="18" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C16" s="17">
         <v>1053.9846</v>
@@ -18574,10 +20236,18 @@
         <f>SUM(C16:J16)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L16" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H16/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="19">
+        <f>IF(G16=0,"n/a",(H16-G16)/G16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C17" s="28">
         <v>687.6974</v>
@@ -18607,10 +20277,18 @@
         <f>SUM(C17:J17)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L17" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H17/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="19">
+        <f>IF(G17=0,"n/a",(H17-G17)/G17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C18" s="17">
         <v>426.923</v>
@@ -18640,10 +20318,18 @@
         <f>SUM(C18:J18)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L18" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H18/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="19">
+        <f>IF(G18=0,"n/a",(H18-G18)/G18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C19" s="28">
         <v>346.8787</v>
@@ -18673,10 +20359,18 @@
         <f>SUM(C19:J19)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L19" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H19/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="19">
+        <f>IF(G19=0,"n/a",(H19-G19)/G19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B20" s="18" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C20" s="17">
         <v>152.0005</v>
@@ -18706,10 +20400,18 @@
         <f>SUM(C20:J20)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L20" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H20/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="19">
+        <f>IF(G20=0,"n/a",(H20-G20)/G20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C21" s="28">
         <v>255.309</v>
@@ -18739,10 +20441,18 @@
         <f>SUM(C21:J21)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L21" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H21/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="19">
+        <f>IF(G21=0,"n/a",(H21-G21)/G21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C22" s="17">
         <v>41.7791</v>
@@ -18772,10 +20482,18 @@
         <f>SUM(C22:J22)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L22" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H22/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="19">
+        <f>IF(G22=0,"n/a",(H22-G22)/G22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23" s="18" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C23" s="28">
         <v>0</v>
@@ -18805,10 +20523,18 @@
         <f>SUM(C23:J23)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L23" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H23/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="19">
+        <f>IF(G23=0,"n/a",(H23-G23)/G23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B24" s="18" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C24" s="17">
         <v>0</v>
@@ -18838,12 +20564,20 @@
         <f>SUM(C24:J24)</f>
         <v>0</v>
       </c>
+      <c r="L24" s="19">
+        <f>IF(SUM(H8:H24)=0,0,H24/SUM(H8:H24))</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="19">
+        <f>IF(G24=0,"n/a",(H24-G24)/G24)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="B6:M6"/>
   </mergeCells>
   <conditionalFormatting sqref="K8:K24">
     <cfRule type="dataBar" priority="1">
@@ -18902,7 +20636,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -18913,7 +20647,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -18924,7 +20658,7 @@
     </row>
     <row r="6" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -18935,36 +20669,36 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C7" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>53</v>
-      </c>
       <c r="G7" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="18" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E8" s="17">
         <v>33211.3093</v>
@@ -18981,13 +20715,13 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="18" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E9" s="17">
         <v>23493.4786</v>
@@ -19004,13 +20738,13 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="18" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="E10" s="17">
         <v>23153.0157</v>
@@ -19027,13 +20761,13 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="18" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E11" s="17">
         <v>21904.0436</v>
@@ -19050,13 +20784,13 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="18" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E12" s="17">
         <v>19129.417</v>
@@ -19073,13 +20807,13 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="18" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E13" s="17">
         <v>17686.618</v>
@@ -19096,13 +20830,13 @@
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="18" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E14" s="17">
         <v>16687.4264</v>
@@ -19119,13 +20853,13 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="18" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E15" s="17">
         <v>16208.9322</v>
@@ -19142,13 +20876,13 @@
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="18" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E16" s="17">
         <v>14425.3208</v>
@@ -19165,13 +20899,13 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="18" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E17" s="17">
         <v>13588.9185</v>
@@ -19188,13 +20922,13 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="18" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E18" s="17">
         <v>13501.072</v>
@@ -19211,13 +20945,13 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="18" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E19" s="17">
         <v>13331.4763</v>
@@ -19234,13 +20968,13 @@
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="18" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E20" s="17">
         <v>13291.4389</v>
@@ -19257,13 +20991,13 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="18" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E21" s="17">
         <v>13290.7522</v>
@@ -19280,13 +21014,13 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E22" s="17">
         <v>12949.1048</v>
@@ -19303,7 +21037,7 @@
     </row>
     <row r="25" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -19316,7 +21050,7 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="14" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C26" s="16">
         <v>2020</v>
@@ -19345,7 +21079,7 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C27" s="17">
         <v>25306.5576</v>
@@ -19374,7 +21108,7 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="18" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C28" s="28">
         <v>21532.9607</v>
@@ -19403,7 +21137,7 @@
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="18" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C29" s="17">
         <v>17593.7547</v>
@@ -19432,7 +21166,7 @@
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="18" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C30" s="28">
         <v>11989.8758</v>
@@ -19461,7 +21195,7 @@
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C31" s="17">
         <v>11627.2754</v>
@@ -19490,7 +21224,7 @@
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="18" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C32" s="28">
         <v>11065.1157</v>
@@ -19519,7 +21253,7 @@
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="18" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C33" s="17">
         <v>3368.9389</v>
@@ -19548,7 +21282,7 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="18" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C34" s="28">
         <v>3352.229</v>
@@ -19577,7 +21311,7 @@
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="18" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C35" s="17">
         <v>5949.0325</v>
@@ -19606,7 +21340,7 @@
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="18" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C36" s="28">
         <v>1831.612</v>
@@ -19635,7 +21369,7 @@
     </row>
     <row r="39" spans="2:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="7" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
@@ -19643,10 +21377,10 @@
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
@@ -22897,22 +24631,23 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FFC00000"/>
+    <tabColor rgb="FF843C0C"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:N61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B2:O69"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="14" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="14" width="8.28515625" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -22926,10 +24661,11 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
-    </row>
-    <row r="3" spans="2:14">
+      <c r="O2" s="1"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -22943,830 +24679,1751 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
-    </row>
-    <row r="6" spans="2:14" ht="20" customHeight="1">
-      <c r="B6" s="5" t="s">
+      <c r="O3" s="2"/>
+    </row>
+    <row r="6" spans="2:15" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="N7" s="15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B8" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" s="31">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="D8" s="31">
+        <v>19.8</v>
+      </c>
+      <c r="E8" s="31">
+        <v>110</v>
+      </c>
+      <c r="F8" s="31">
+        <v>40.7</v>
+      </c>
+      <c r="G8" s="31">
+        <v>52.8</v>
+      </c>
+      <c r="H8" s="31">
+        <v>69.3</v>
+      </c>
+      <c r="I8" s="31">
+        <v>0</v>
+      </c>
+      <c r="J8" s="31">
+        <v>0</v>
+      </c>
+      <c r="K8" s="31">
+        <v>0</v>
+      </c>
+      <c r="L8" s="31">
+        <v>0</v>
+      </c>
+      <c r="M8" s="31">
+        <v>0</v>
+      </c>
+      <c r="N8" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B9" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" s="31">
+        <v>0</v>
+      </c>
+      <c r="D9" s="31">
+        <v>19.8</v>
+      </c>
+      <c r="E9" s="31">
+        <v>55.33</v>
+      </c>
+      <c r="F9" s="31">
+        <v>0</v>
+      </c>
+      <c r="G9" s="31">
+        <v>0</v>
+      </c>
+      <c r="H9" s="31">
+        <v>0</v>
+      </c>
+      <c r="I9" s="31">
+        <v>42.9</v>
+      </c>
+      <c r="J9" s="31">
+        <v>17.6</v>
+      </c>
+      <c r="K9" s="31">
+        <v>0</v>
+      </c>
+      <c r="L9" s="31">
+        <v>0</v>
+      </c>
+      <c r="M9" s="31">
+        <v>0</v>
+      </c>
+      <c r="N9" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B10" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="31">
+        <v>28.6</v>
+      </c>
+      <c r="D10" s="31">
+        <v>110</v>
+      </c>
+      <c r="E10" s="31">
+        <v>0</v>
+      </c>
+      <c r="F10" s="31">
+        <v>0</v>
+      </c>
+      <c r="G10" s="31">
+        <v>6.4</v>
+      </c>
+      <c r="H10" s="31">
+        <v>8</v>
+      </c>
+      <c r="I10" s="31">
+        <v>12.64</v>
+      </c>
+      <c r="J10" s="31">
+        <v>0</v>
+      </c>
+      <c r="K10" s="31">
+        <v>11</v>
+      </c>
+      <c r="L10" s="31">
+        <v>0</v>
+      </c>
+      <c r="M10" s="31">
+        <v>0</v>
+      </c>
+      <c r="N10" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B11" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C11" s="31">
+        <v>0</v>
+      </c>
+      <c r="D11" s="31">
+        <v>0</v>
+      </c>
+      <c r="E11" s="31">
+        <v>17.6</v>
+      </c>
+      <c r="F11" s="31">
+        <v>7.7</v>
+      </c>
+      <c r="G11" s="31">
+        <v>0</v>
+      </c>
+      <c r="H11" s="31">
+        <v>0</v>
+      </c>
+      <c r="I11" s="31">
+        <v>0</v>
+      </c>
+      <c r="J11" s="31">
+        <v>0</v>
+      </c>
+      <c r="K11" s="31">
+        <v>0</v>
+      </c>
+      <c r="L11" s="31">
+        <v>0</v>
+      </c>
+      <c r="M11" s="31">
+        <v>0</v>
+      </c>
+      <c r="N11" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B12" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="31">
+        <v>0</v>
+      </c>
+      <c r="D12" s="31">
+        <v>0</v>
+      </c>
+      <c r="E12" s="31">
+        <v>0</v>
+      </c>
+      <c r="F12" s="31">
+        <v>0</v>
+      </c>
+      <c r="G12" s="31">
+        <v>0</v>
+      </c>
+      <c r="H12" s="31">
+        <v>0</v>
+      </c>
+      <c r="I12" s="31">
+        <v>0</v>
+      </c>
+      <c r="J12" s="31">
+        <v>0</v>
+      </c>
+      <c r="K12" s="31">
+        <v>0</v>
+      </c>
+      <c r="L12" s="31">
+        <v>2.7</v>
+      </c>
+      <c r="M12" s="31">
+        <v>15.3</v>
+      </c>
+      <c r="N12" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13" s="31">
+        <v>5.4</v>
+      </c>
+      <c r="D13" s="31">
+        <v>90</v>
+      </c>
+      <c r="E13" s="31">
+        <v>37.8</v>
+      </c>
+      <c r="F13" s="31">
+        <v>0</v>
+      </c>
+      <c r="G13" s="31">
+        <v>0</v>
+      </c>
+      <c r="H13" s="31">
+        <v>6.3</v>
+      </c>
+      <c r="I13" s="31">
+        <v>0</v>
+      </c>
+      <c r="J13" s="31">
+        <v>0</v>
+      </c>
+      <c r="K13" s="31">
+        <v>0</v>
+      </c>
+      <c r="L13" s="31">
+        <v>0</v>
+      </c>
+      <c r="M13" s="31">
+        <v>0</v>
+      </c>
+      <c r="N13" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="31">
+        <v>1.3</v>
+      </c>
+      <c r="D14" s="31">
+        <v>0</v>
+      </c>
+      <c r="E14" s="31">
+        <v>0</v>
+      </c>
+      <c r="F14" s="31">
+        <v>0</v>
+      </c>
+      <c r="G14" s="31">
+        <v>16.25</v>
+      </c>
+      <c r="H14" s="31">
+        <v>0</v>
+      </c>
+      <c r="I14" s="31">
+        <v>0</v>
+      </c>
+      <c r="J14" s="31">
+        <v>0</v>
+      </c>
+      <c r="K14" s="31">
+        <v>0</v>
+      </c>
+      <c r="L14" s="31">
+        <v>0</v>
+      </c>
+      <c r="M14" s="31">
+        <v>0</v>
+      </c>
+      <c r="N14" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B15" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C15" s="31">
+        <v>0</v>
+      </c>
+      <c r="D15" s="31">
+        <v>0</v>
+      </c>
+      <c r="E15" s="31">
+        <v>0</v>
+      </c>
+      <c r="F15" s="31">
+        <v>0</v>
+      </c>
+      <c r="G15" s="31">
+        <v>0</v>
+      </c>
+      <c r="H15" s="31">
+        <v>0</v>
+      </c>
+      <c r="I15" s="31">
+        <v>0</v>
+      </c>
+      <c r="J15" s="31">
+        <v>0</v>
+      </c>
+      <c r="K15" s="31">
+        <v>0</v>
+      </c>
+      <c r="L15" s="31">
+        <v>0</v>
+      </c>
+      <c r="M15" s="31">
+        <v>0</v>
+      </c>
+      <c r="N15" s="31">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B16" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="31">
+        <v>104.4</v>
+      </c>
+      <c r="D16" s="31">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="E16" s="31">
+        <v>0</v>
+      </c>
+      <c r="F16" s="31">
+        <v>0</v>
+      </c>
+      <c r="G16" s="31">
+        <v>0</v>
+      </c>
+      <c r="H16" s="31">
+        <v>0</v>
+      </c>
+      <c r="I16" s="31">
+        <v>0</v>
+      </c>
+      <c r="J16" s="31">
+        <v>0</v>
+      </c>
+      <c r="K16" s="31">
+        <v>2.04</v>
+      </c>
+      <c r="L16" s="31">
+        <v>0</v>
+      </c>
+      <c r="M16" s="31">
+        <v>0</v>
+      </c>
+      <c r="N16" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B17" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C17" s="31">
+        <v>0</v>
+      </c>
+      <c r="D17" s="31">
+        <v>0</v>
+      </c>
+      <c r="E17" s="31">
+        <v>0</v>
+      </c>
+      <c r="F17" s="31">
+        <v>0</v>
+      </c>
+      <c r="G17" s="31">
+        <v>0</v>
+      </c>
+      <c r="H17" s="31">
+        <v>60</v>
+      </c>
+      <c r="I17" s="31">
+        <v>0</v>
+      </c>
+      <c r="J17" s="31">
+        <v>0</v>
+      </c>
+      <c r="K17" s="31">
+        <v>0</v>
+      </c>
+      <c r="L17" s="31">
+        <v>0</v>
+      </c>
+      <c r="M17" s="31">
+        <v>0</v>
+      </c>
+      <c r="N17" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18" s="31">
+        <v>0</v>
+      </c>
+      <c r="D18" s="31">
+        <v>0</v>
+      </c>
+      <c r="E18" s="31">
+        <v>0</v>
+      </c>
+      <c r="F18" s="31">
+        <v>0</v>
+      </c>
+      <c r="G18" s="31">
+        <v>15.6</v>
+      </c>
+      <c r="H18" s="31">
+        <v>0</v>
+      </c>
+      <c r="I18" s="31">
+        <v>0</v>
+      </c>
+      <c r="J18" s="31">
+        <v>0</v>
+      </c>
+      <c r="K18" s="31">
+        <v>0</v>
+      </c>
+      <c r="L18" s="31">
+        <v>0</v>
+      </c>
+      <c r="M18" s="31">
+        <v>0</v>
+      </c>
+      <c r="N18" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B19" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="C19" s="31">
+        <v>0</v>
+      </c>
+      <c r="D19" s="31">
+        <v>0</v>
+      </c>
+      <c r="E19" s="31">
+        <v>0</v>
+      </c>
+      <c r="F19" s="31">
+        <v>28.46</v>
+      </c>
+      <c r="G19" s="31">
+        <v>0</v>
+      </c>
+      <c r="H19" s="31">
+        <v>0</v>
+      </c>
+      <c r="I19" s="31">
+        <v>0</v>
+      </c>
+      <c r="J19" s="31">
+        <v>0</v>
+      </c>
+      <c r="K19" s="31">
+        <v>0</v>
+      </c>
+      <c r="L19" s="31">
+        <v>0</v>
+      </c>
+      <c r="M19" s="31">
+        <v>0</v>
+      </c>
+      <c r="N19" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B20" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="31">
+        <v>0</v>
+      </c>
+      <c r="D20" s="31">
+        <v>0</v>
+      </c>
+      <c r="E20" s="31">
+        <v>34.3</v>
+      </c>
+      <c r="F20" s="31">
+        <v>61.74</v>
+      </c>
+      <c r="G20" s="31">
+        <v>0</v>
+      </c>
+      <c r="H20" s="31">
+        <v>0</v>
+      </c>
+      <c r="I20" s="31">
+        <v>0</v>
+      </c>
+      <c r="J20" s="31">
+        <v>0</v>
+      </c>
+      <c r="K20" s="31">
+        <v>0</v>
+      </c>
+      <c r="L20" s="31">
+        <v>0</v>
+      </c>
+      <c r="M20" s="31">
+        <v>0</v>
+      </c>
+      <c r="N20" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B21" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="31">
+        <v>0</v>
+      </c>
+      <c r="D21" s="31">
+        <v>0</v>
+      </c>
+      <c r="E21" s="31">
+        <v>0</v>
+      </c>
+      <c r="F21" s="31">
+        <v>98</v>
+      </c>
+      <c r="G21" s="31">
+        <v>66.64</v>
+      </c>
+      <c r="H21" s="31">
+        <v>0</v>
+      </c>
+      <c r="I21" s="31">
+        <v>53.9</v>
+      </c>
+      <c r="J21" s="31">
+        <v>31.36</v>
+      </c>
+      <c r="K21" s="31">
+        <v>0</v>
+      </c>
+      <c r="L21" s="31">
+        <v>2.94</v>
+      </c>
+      <c r="M21" s="31">
+        <v>0</v>
+      </c>
+      <c r="N21" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B22" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" s="31">
+        <v>0</v>
+      </c>
+      <c r="D22" s="31">
+        <v>16.34</v>
+      </c>
+      <c r="E22" s="31">
+        <v>16.8</v>
+      </c>
+      <c r="F22" s="31">
+        <v>15.4</v>
+      </c>
+      <c r="G22" s="31">
+        <v>9.31</v>
+      </c>
+      <c r="H22" s="31">
+        <v>0</v>
+      </c>
+      <c r="I22" s="31">
+        <v>0</v>
+      </c>
+      <c r="J22" s="31">
+        <v>0</v>
+      </c>
+      <c r="K22" s="31">
+        <v>0</v>
+      </c>
+      <c r="L22" s="31">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M22" s="31">
+        <v>0</v>
+      </c>
+      <c r="N22" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B23" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="31">
+        <v>0</v>
+      </c>
+      <c r="D23" s="31">
+        <v>17.5</v>
+      </c>
+      <c r="E23" s="31">
+        <v>25</v>
+      </c>
+      <c r="F23" s="31">
+        <v>17.74</v>
+      </c>
+      <c r="G23" s="31">
+        <v>38.22</v>
+      </c>
+      <c r="H23" s="31">
+        <v>18.9</v>
+      </c>
+      <c r="I23" s="31">
+        <v>0</v>
+      </c>
+      <c r="J23" s="31">
+        <v>0</v>
+      </c>
+      <c r="K23" s="31">
+        <v>0</v>
+      </c>
+      <c r="L23" s="31">
+        <v>0</v>
+      </c>
+      <c r="M23" s="31">
+        <v>0</v>
+      </c>
+      <c r="N23" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B27" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B28" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="16">
+        <v>2022</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="F28" s="17">
+        <v>6</v>
+      </c>
+      <c r="G28" s="17">
+        <v>385</v>
+      </c>
+      <c r="H28" s="19">
+        <v>0.5571428571428572</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B29" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="16">
+        <v>2019</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="F29" s="17">
+        <v>6</v>
+      </c>
+      <c r="G29" s="17">
+        <v>218.54</v>
+      </c>
+      <c r="H29" s="19">
+        <v>0.8229157133705501</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B30" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="20">
+        <v>2026</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="F30" s="17">
+        <v>5</v>
+      </c>
+      <c r="G30" s="17">
+        <v>117.36</v>
+      </c>
+      <c r="H30" s="19">
+        <v>0.7443762781186092</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B31" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="16">
+        <v>2015</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="F31" s="17">
+        <v>4</v>
+      </c>
+      <c r="G31" s="17">
+        <v>320.1</v>
+      </c>
+      <c r="H31" s="19">
+        <v>0.2783505154639175</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B32" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="16">
+        <v>2014</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="F32" s="17">
+        <v>4</v>
+      </c>
+      <c r="G32" s="17">
+        <v>294</v>
+      </c>
+      <c r="H32" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" s="16">
+        <v>2014</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="F33" s="17">
+        <v>4</v>
+      </c>
+      <c r="G33" s="17">
+        <v>290</v>
+      </c>
+      <c r="H33" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34" s="16">
+        <v>2017</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="F34" s="17">
+        <v>4</v>
+      </c>
+      <c r="G34" s="17">
+        <v>263.775</v>
+      </c>
+      <c r="H34" s="19">
+        <v>0.007108330963889679</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" s="16">
+        <v>2019</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="F35" s="17">
+        <v>4</v>
+      </c>
+      <c r="G35" s="17">
+        <v>263.62</v>
+      </c>
+      <c r="H35" s="19">
+        <v>0.02230483271375465</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B36" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" s="16">
+        <v>2025</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="F36" s="17">
+        <v>4</v>
+      </c>
+      <c r="G36" s="17">
+        <v>57.84999999999999</v>
+      </c>
+      <c r="H36" s="19">
+        <v>0.4433880726015558</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D37" s="16">
+        <v>2017</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="F37" s="17">
+        <v>3</v>
+      </c>
+      <c r="G37" s="17">
+        <v>383.9</v>
+      </c>
+      <c r="H37" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B38" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="16">
+        <v>2011</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="F38" s="17">
+        <v>3</v>
+      </c>
+      <c r="G38" s="17">
+        <v>214.83</v>
+      </c>
+      <c r="H38" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B39" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D39" s="20">
+        <v>2027</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="F39" s="17">
+        <v>3</v>
+      </c>
+      <c r="G39" s="17">
+        <v>210</v>
+      </c>
+      <c r="H39" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" s="16">
+        <v>2018</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="F40" s="17">
+        <v>3</v>
+      </c>
+      <c r="G40" s="17">
+        <v>207.1875</v>
+      </c>
+      <c r="H40" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" s="16">
+        <v>2013</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="F41" s="17">
+        <v>3</v>
+      </c>
+      <c r="G41" s="17">
+        <v>179.55</v>
+      </c>
+      <c r="H41" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B42" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D42" s="16">
+        <v>2015</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F42" s="17">
+        <v>3</v>
+      </c>
+      <c r="G42" s="17">
+        <v>178.8</v>
+      </c>
+      <c r="H42" s="19">
+        <v>0.2214765100671141</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B43" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="16">
+        <v>2023</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="F43" s="17">
+        <v>3</v>
+      </c>
+      <c r="G43" s="17">
+        <v>133.2</v>
+      </c>
+      <c r="H43" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B44" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="16">
+        <v>2017</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="F44" s="17">
+        <v>3</v>
+      </c>
+      <c r="G44" s="17">
+        <v>54.88000000000001</v>
+      </c>
+      <c r="H44" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B45" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D45" s="16">
+        <v>2024</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="F45" s="17">
+        <v>3</v>
+      </c>
+      <c r="G45" s="17">
+        <v>27.04</v>
+      </c>
+      <c r="H45" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B49" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="G49" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E50" s="16">
+        <v>2022</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G50" s="17">
+        <v>12</v>
+      </c>
+      <c r="H50" s="17">
+        <v>7735.68</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" s="16">
+        <v>2023</v>
+      </c>
+      <c r="F51" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G51" s="17">
+        <v>12</v>
+      </c>
+      <c r="H51" s="17">
+        <v>2741.615</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="D52" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E52" s="16">
+        <v>2015</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G52" s="17">
+        <v>12</v>
+      </c>
+      <c r="H52" s="17">
+        <v>2303.12</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" s="16">
+        <v>2023</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G53" s="17">
+        <v>12</v>
+      </c>
+      <c r="H53" s="17">
+        <v>2094.516</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="D54" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E54" s="16">
+        <v>2022</v>
+      </c>
+      <c r="F54" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G54" s="17">
+        <v>12</v>
+      </c>
+      <c r="H54" s="17">
+        <v>1948.378</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B55" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E55" s="16">
+        <v>2024</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G55" s="17">
+        <v>12</v>
+      </c>
+      <c r="H55" s="17">
+        <v>1725.83</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B56" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D56" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E56" s="16">
+        <v>2023</v>
+      </c>
+      <c r="F56" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G56" s="17">
+        <v>12</v>
+      </c>
+      <c r="H56" s="17">
+        <v>1674.745</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="C57" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="2:14">
-      <c r="B7" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-    </row>
-    <row r="8" spans="2:14">
-      <c r="B8" s="30" t="s">
-        <v>178</v>
-      </c>
-      <c r="C8" s="32">
-        <v>0</v>
-      </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-    </row>
-    <row r="9" spans="2:14">
-      <c r="B9" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="33">
-        <v>1</v>
-      </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-    </row>
-    <row r="10" spans="2:14">
-      <c r="B10" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="C10" s="34">
-        <v>0</v>
-      </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-    </row>
-    <row r="11" spans="2:14">
-      <c r="B11" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-    </row>
-    <row r="13" spans="2:14" ht="20" customHeight="1">
-      <c r="B13" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-    </row>
-    <row r="14" spans="2:14">
-      <c r="B14" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="M14" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="N14" s="15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14">
-      <c r="B15" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="C15" s="17">
-        <v>2282.61105</v>
-      </c>
-      <c r="D15" s="17">
-        <v>3072.01685</v>
-      </c>
-      <c r="E15" s="17">
-        <v>2313.48415</v>
-      </c>
-      <c r="F15" s="17">
-        <v>2274.507825</v>
-      </c>
-      <c r="G15" s="17">
-        <v>1589.601875</v>
-      </c>
-      <c r="H15" s="17">
-        <v>1370.05175</v>
-      </c>
-      <c r="I15" s="17">
-        <v>1306.436325</v>
-      </c>
-      <c r="J15" s="17">
-        <v>1245.677625</v>
-      </c>
-      <c r="K15" s="17">
-        <v>1515.4383</v>
-      </c>
-      <c r="L15" s="17">
-        <v>2050.317675</v>
-      </c>
-      <c r="M15" s="17">
-        <v>1344.783825</v>
-      </c>
-      <c r="N15" s="17">
-        <v>1425.26985</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14">
-      <c r="B16" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="C16" s="17">
-        <v>2331.3456</v>
-      </c>
-      <c r="D16" s="17">
-        <v>3242.643133333333</v>
-      </c>
-      <c r="E16" s="17">
-        <v>2452.0467</v>
-      </c>
-      <c r="F16" s="17">
-        <v>2323.8248</v>
-      </c>
-      <c r="G16" s="17">
-        <v>1480.8669</v>
-      </c>
-      <c r="H16" s="17">
-        <v>1371.5984</v>
-      </c>
-      <c r="I16" s="17">
-        <v>1295.816366666667</v>
-      </c>
-      <c r="J16" s="17">
-        <v>1211.909366666667</v>
-      </c>
-      <c r="K16" s="17">
-        <v>1621.180633333333</v>
-      </c>
-      <c r="L16" s="17">
-        <v>2132.550833333333</v>
-      </c>
-      <c r="M16" s="17">
-        <v>1240.659633333333</v>
-      </c>
-      <c r="N16" s="17">
-        <v>806.3173666666667</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14">
-      <c r="B17" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="C17" s="17">
-        <v>1933.502583333333</v>
-      </c>
-      <c r="D17" s="17">
-        <v>2767.98955</v>
-      </c>
-      <c r="E17" s="17">
-        <v>2082.86935</v>
-      </c>
-      <c r="F17" s="17">
-        <v>2054.312466666667</v>
-      </c>
-      <c r="G17" s="17">
-        <v>1459.746016666667</v>
-      </c>
-      <c r="H17" s="17">
-        <v>1224.888666666667</v>
-      </c>
-      <c r="I17" s="17">
-        <v>1258.94175</v>
-      </c>
-      <c r="J17" s="17">
-        <v>1115.338283333333</v>
-      </c>
-      <c r="K17" s="17">
-        <v>1463.838083333333</v>
-      </c>
-      <c r="L17" s="17">
-        <v>1795.539</v>
-      </c>
-      <c r="M17" s="17">
-        <v>1192.92015</v>
-      </c>
-      <c r="N17" s="17">
-        <v>1127.578033333333</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14">
-      <c r="B18" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="C18" s="17">
-        <v>1643.7977</v>
-      </c>
-      <c r="D18" s="17">
-        <v>2083.21442</v>
-      </c>
-      <c r="E18" s="17">
-        <v>1614.52331</v>
-      </c>
-      <c r="F18" s="17">
-        <v>1584.22778</v>
-      </c>
-      <c r="G18" s="17">
-        <v>1154.09354</v>
-      </c>
-      <c r="H18" s="17">
-        <v>997.7466400000001</v>
-      </c>
-      <c r="I18" s="17">
-        <v>999.65198</v>
-      </c>
-      <c r="J18" s="17">
-        <v>1210.45329</v>
-      </c>
-      <c r="K18" s="17">
-        <v>1988.70389</v>
-      </c>
-      <c r="L18" s="17">
-        <v>1586.17207</v>
-      </c>
-      <c r="M18" s="17">
-        <v>1044.36847</v>
-      </c>
-      <c r="N18" s="17">
-        <v>916.2710999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14" ht="20" customHeight="1">
-      <c r="B20" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-    </row>
-    <row r="21" spans="2:14">
-      <c r="B21" s="14"/>
-      <c r="C21" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="J21" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="L21" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="M21" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="N21" s="15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14">
-      <c r="B22" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="C22" s="17">
-        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),1)</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="17">
-        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),2)</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="17">
-        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),3)</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="17">
-        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),4)</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="17">
-        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),5)</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="17">
-        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),6)</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="17">
-        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),7)</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="17">
-        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),8)</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="17">
-        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),9)</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="17">
-        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),10)</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="17">
-        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),11)</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="17">
-        <f>INDEX($C$15:$N$18,MATCH($C$7,$B$15:$B$18,0),12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14">
-      <c r="B23" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="C23" s="35">
-        <f>C22*(1+$C$8)*$C$9+IF($C$11=C21,$C$10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="35">
-        <f>D22*(1+$C$8)*$C$9+IF($C$11=D21,$C$10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="35">
-        <f>E22*(1+$C$8)*$C$9+IF($C$11=E21,$C$10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="35">
-        <f>F22*(1+$C$8)*$C$9+IF($C$11=F21,$C$10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="35">
-        <f>G22*(1+$C$8)*$C$9+IF($C$11=G21,$C$10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="35">
-        <f>H22*(1+$C$8)*$C$9+IF($C$11=H21,$C$10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="35">
-        <f>I22*(1+$C$8)*$C$9+IF($C$11=I21,$C$10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="35">
-        <f>J22*(1+$C$8)*$C$9+IF($C$11=J21,$C$10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="35">
-        <f>K22*(1+$C$8)*$C$9+IF($C$11=K21,$C$10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L23" s="35">
-        <f>L22*(1+$C$8)*$C$9+IF($C$11=L21,$C$10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="M23" s="35">
-        <f>M22*(1+$C$8)*$C$9+IF($C$11=M21,$C$10,0)</f>
-        <v>0</v>
-      </c>
-      <c r="N23" s="35">
-        <f>N22*(1+$C$8)*$C$9+IF($C$11=N21,$C$10,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14" ht="20" customHeight="1">
-      <c r="B25" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="2:14">
-      <c r="B26" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="C26" s="17">
-        <f>SUM(C22:N22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14">
-      <c r="B27" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="C27" s="35">
-        <f>SUM(C23:N23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14">
-      <c r="B28" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="C28" s="36">
-        <v>15923.1696</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14">
-      <c r="B29" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="C29" s="35">
-        <f>$C$27+$C$28</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" ht="20" customHeight="1">
-      <c r="B31" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-    </row>
-    <row r="32" spans="2:14">
-      <c r="B32" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="I32" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="J32" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="L32" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="M32" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="N32" s="15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14">
-      <c r="B33" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="C33" s="17">
-        <f>C23</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="17">
-        <f>D23</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="17">
-        <f>E23</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="17">
-        <f>F23</f>
-        <v>0</v>
-      </c>
-      <c r="G33" s="17">
-        <f>G23</f>
-        <v>0</v>
-      </c>
-      <c r="H33" s="17">
-        <f>H23</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="17">
-        <f>I23</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="17">
-        <f>J23</f>
-        <v>0</v>
-      </c>
-      <c r="K33" s="17">
-        <f>K23</f>
-        <v>0</v>
-      </c>
-      <c r="L33" s="17">
-        <f>L23</f>
-        <v>0</v>
-      </c>
-      <c r="M33" s="17">
-        <f>M23</f>
-        <v>0</v>
-      </c>
-      <c r="N33" s="17">
-        <f>N23</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:14">
-      <c r="B34" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C34" s="17">
-        <v>1088.333</v>
-      </c>
-      <c r="D34" s="17">
-        <v>2092.4001</v>
-      </c>
-      <c r="E34" s="17">
-        <v>2910.1523</v>
-      </c>
-      <c r="F34" s="17">
-        <v>2004.0124</v>
-      </c>
-      <c r="G34" s="17">
-        <v>901.152</v>
-      </c>
-      <c r="H34" s="17">
-        <v>215.305</v>
-      </c>
-      <c r="I34" s="17">
-        <v>167.5</v>
-      </c>
-      <c r="J34" s="17">
-        <v>51.06</v>
-      </c>
-      <c r="K34" s="17">
-        <v>2986.8719</v>
-      </c>
-      <c r="L34" s="17">
-        <v>2955.9469</v>
-      </c>
-      <c r="M34" s="17">
-        <v>546.936</v>
-      </c>
-      <c r="N34" s="17">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="35" spans="2:14">
-      <c r="B35" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="C35" s="17">
-        <v>1400.9949</v>
-      </c>
-      <c r="D35" s="17">
-        <v>2023.3805</v>
-      </c>
-      <c r="E35" s="17">
-        <v>2228.4465</v>
-      </c>
-      <c r="F35" s="17">
-        <v>2621.2351</v>
-      </c>
-      <c r="G35" s="17">
-        <v>1753.1826</v>
-      </c>
-      <c r="H35" s="17">
-        <v>1169.5851</v>
-      </c>
-      <c r="I35" s="17">
-        <v>939.4538</v>
-      </c>
-      <c r="J35" s="17">
-        <v>979.7175</v>
-      </c>
-      <c r="K35" s="17">
-        <v>1487.0255</v>
-      </c>
-      <c r="L35" s="17">
-        <v>2468.751</v>
-      </c>
-      <c r="M35" s="17">
-        <v>1324.048</v>
-      </c>
-      <c r="N35" s="17">
-        <v>861.7330000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="2:14">
-      <c r="B36" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="C36" s="17">
-        <v>2433.6238</v>
-      </c>
-      <c r="D36" s="17">
-        <v>5025.1422</v>
-      </c>
-      <c r="E36" s="17">
-        <v>2051.1556</v>
-      </c>
-      <c r="F36" s="17">
-        <v>1881.5364</v>
-      </c>
-      <c r="G36" s="17">
-        <v>940.6905</v>
-      </c>
-      <c r="H36" s="17">
-        <v>1023.714</v>
-      </c>
-      <c r="I36" s="17">
-        <v>1472.8685</v>
-      </c>
-      <c r="J36" s="17">
-        <v>1211.9996</v>
-      </c>
-      <c r="K36" s="17">
-        <v>1844.9944</v>
-      </c>
-      <c r="L36" s="17">
-        <v>1940.158</v>
-      </c>
-      <c r="M36" s="17">
-        <v>1047.007</v>
-      </c>
-      <c r="N36" s="17">
-        <v>709.6768</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" ht="20" customHeight="1">
-      <c r="B55" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-    </row>
-    <row r="56" spans="2:4">
-      <c r="B56" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4">
-      <c r="B57" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="C57" s="37">
-        <v>0.04589747951384983</v>
-      </c>
-      <c r="D57" s="36">
-        <f>$C$27*C57</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4">
+      <c r="D57" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E57" s="16">
+        <v>2019</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G57" s="17">
+        <v>12</v>
+      </c>
+      <c r="H57" s="17">
+        <v>1604.4</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B58" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C58" s="37">
-        <v>0.2506235705412687</v>
-      </c>
-      <c r="D58" s="36">
-        <f>$C$27*C58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4">
+        <v>226</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="D58" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E58" s="16">
+        <v>2022</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G58" s="17">
+        <v>12</v>
+      </c>
+      <c r="H58" s="17">
+        <v>1604.4</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B59" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C59" s="37">
-        <v>0.4704779391371361</v>
-      </c>
-      <c r="D59" s="36">
-        <f>$C$27*C59</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4">
+        <v>156</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E59" s="16">
+        <v>2015</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G59" s="17">
+        <v>12</v>
+      </c>
+      <c r="H59" s="17">
+        <v>1482.4687</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B60" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D60" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E60" s="16">
+        <v>2014</v>
+      </c>
+      <c r="F60" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G60" s="17">
+        <v>12</v>
+      </c>
+      <c r="H60" s="17">
+        <v>1184.2962</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B61" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="D61" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="37">
-        <v>0.0338183058472656</v>
-      </c>
-      <c r="D60" s="36">
-        <f>$C$27*C60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4">
-      <c r="B61" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C61" s="37">
-        <v>0.1991827049604797</v>
-      </c>
-      <c r="D61" s="36">
-        <f>$C$27*C61</f>
-        <v>0</v>
+      <c r="E61" s="16">
+        <v>2023</v>
+      </c>
+      <c r="F61" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G61" s="17">
+        <v>12</v>
+      </c>
+      <c r="H61" s="17">
+        <v>1043.455</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B62" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="D62" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E62" s="16">
+        <v>2019</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G62" s="17">
+        <v>12</v>
+      </c>
+      <c r="H62" s="17">
+        <v>1032.846</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B63" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D63" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E63" s="16">
+        <v>2014</v>
+      </c>
+      <c r="F63" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G63" s="17">
+        <v>12</v>
+      </c>
+      <c r="H63" s="17">
+        <v>986.4872000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B64" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E64" s="16">
+        <v>2014</v>
+      </c>
+      <c r="F64" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G64" s="17">
+        <v>12</v>
+      </c>
+      <c r="H64" s="17">
+        <v>957.53</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B65" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="D65" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E65" s="16">
+        <v>2012</v>
+      </c>
+      <c r="F65" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G65" s="17">
+        <v>12</v>
+      </c>
+      <c r="H65" s="17">
+        <v>885.53</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B66" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E66" s="16">
+        <v>2022</v>
+      </c>
+      <c r="F66" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G66" s="17">
+        <v>12</v>
+      </c>
+      <c r="H66" s="17">
+        <v>875.554</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B67" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="D67" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E67" s="16">
+        <v>2013</v>
+      </c>
+      <c r="F67" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G67" s="17">
+        <v>12</v>
+      </c>
+      <c r="H67" s="17">
+        <v>846.235</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B68" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="D68" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E68" s="16">
+        <v>2011</v>
+      </c>
+      <c r="F68" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G68" s="17">
+        <v>12</v>
+      </c>
+      <c r="H68" s="17">
+        <v>786.3200000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B69" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E69" s="16">
+        <v>2023</v>
+      </c>
+      <c r="F69" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="G69" s="17">
+        <v>12</v>
+      </c>
+      <c r="H69" s="17">
+        <v>715.244</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="B13:N13"/>
-    <mergeCell ref="B20:N20"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B55:D55"/>
+  <mergeCells count="5">
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B3:O3"/>
+    <mergeCell ref="B6:O6"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="B48:I48"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C7">
-      <formula1>"2022-2025,2023-2025,2018-19 &amp; 22-25,All ex-2020/21"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11">
-      <formula1>"Jan,Feb,Mar,Apr,May,Jun,Jul,Aug,Sep,Oct,Nov,Dec"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <conditionalFormatting sqref="C8:N23">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FFED7D31"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28:G45">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFED7D31"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DA7ABA51-AAAA-BBBB-0009-000000000001}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H50:H69">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF1F3864"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DA7ABA51-AAAA-BBBB-0009-000000000002}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" fitToHeight="0" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{DA7ABA51-AAAA-BBBB-0009-000000000001}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" gradient="0" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFED7D31"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G28:G45</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{DA7ABA51-AAAA-BBBB-0009-000000000002}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" gradient="0" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF1F3864"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>H50:H69</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>